--- a/main/ig/ValueSet-fr-core-vs-encounter-identifier-type.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-encounter-identifier-type.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.0.0-ballot</t>
+    <t>2.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -48,7 +48,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>draft</t>
+    <t>active</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-25T10:44:45+00:00</t>
+    <t>2024-03-25T10:59:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-core-vs-encounter-identifier-type.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-encounter-identifier-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-25T10:59:40+00:00</t>
+    <t>2024-03-25T11:06:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-core-vs-encounter-identifier-type.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-encounter-identifier-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-23T08:02:06+00:00</t>
+    <t>2024-05-23T12:05:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-core-vs-encounter-identifier-type.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-encounter-identifier-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-23T12:05:52+00:00</t>
+    <t>2024-05-23T12:32:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-core-vs-encounter-identifier-type.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-encounter-identifier-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-23T12:32:02+00:00</t>
+    <t>2024-05-23T14:35:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-core-vs-encounter-identifier-type.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-encounter-identifier-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-23T14:35:00+00:00</t>
+    <t>2024-06-11T15:33:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-core-vs-encounter-identifier-type.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-encounter-identifier-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-11T15:33:12+00:00</t>
+    <t>2024-06-11T15:33:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-core-vs-encounter-identifier-type.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-encounter-identifier-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-11T15:33:34+00:00</t>
+    <t>2024-07-02T12:51:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -75,7 +75,7 @@
     <t>Interop'Santé (http://interopsante.org/)</t>
   </si>
   <si>
-    <t>InteropSanté (fhir@interopsante.org(WORK))</t>
+    <t>InteropSanté (fhir@interopsante.org(work))</t>
   </si>
   <si>
     <t>Jurisdiction</t>

--- a/main/ig/ValueSet-fr-core-vs-encounter-identifier-type.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-encounter-identifier-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-08T11:39:28+00:00</t>
+    <t>2024-07-17T12:13:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-core-vs-encounter-identifier-type.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-encounter-identifier-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-17T12:13:27+00:00</t>
+    <t>2024-07-17T14:21:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-core-vs-encounter-identifier-type.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-encounter-identifier-type.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.0.1</t>
+    <t>2.1.0-ballot</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-17T14:21:13+00:00</t>
+    <t>2024-07-17T15:15:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-core-vs-encounter-identifier-type.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-encounter-identifier-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-17T15:15:49+00:00</t>
+    <t>2024-07-17T15:35:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-core-vs-encounter-identifier-type.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-encounter-identifier-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-25T07:11:02+00:00</t>
+    <t>2024-07-25T15:28:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-core-vs-encounter-identifier-type.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-encounter-identifier-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-25T15:28:42+00:00</t>
+    <t>2024-07-25T15:29:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-core-vs-encounter-identifier-type.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-encounter-identifier-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-25T15:29:18+00:00</t>
+    <t>2024-07-25T15:44:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-core-vs-encounter-identifier-type.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-encounter-identifier-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-25T15:44:10+00:00</t>
+    <t>2024-08-01T13:12:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-core-vs-encounter-identifier-type.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-encounter-identifier-type.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.1.0-ballot</t>
+    <t>2.1.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-03T15:38:30+00:00</t>
+    <t>2024-09-04T07:28:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-core-vs-encounter-identifier-type.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-encounter-identifier-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-04T07:28:39+00:00</t>
+    <t>2024-09-04T07:33:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-core-vs-encounter-identifier-type.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-encounter-identifier-type.xlsx
@@ -7,7 +7,7 @@
   </bookViews>
   <sheets>
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
-    <sheet name="Include from FR Core CodeSyst" r:id="rId4" sheetId="2"/>
+    <sheet name="Include #0" r:id="rId4" sheetId="2"/>
   </sheets>
 </workbook>
 </file>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-06T12:53:53+00:00</t>
+    <t>2024-10-28T08:07:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-core-vs-encounter-identifier-type.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-encounter-identifier-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-28T08:07:18+00:00</t>
+    <t>2024-10-28T08:08:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-core-vs-encounter-identifier-type.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-encounter-identifier-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-28T08:08:30+00:00</t>
+    <t>2024-10-29T10:42:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-core-vs-encounter-identifier-type.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-encounter-identifier-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-28T09:05:50+00:00</t>
+    <t>2025-01-28T09:07:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-core-vs-encounter-identifier-type.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-encounter-identifier-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-28T09:07:36+00:00</t>
+    <t>2025-02-04T08:51:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-core-vs-encounter-identifier-type.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-encounter-identifier-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-04T08:51:44+00:00</t>
+    <t>2025-02-04T09:30:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-core-vs-encounter-identifier-type.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-encounter-identifier-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-04T09:30:35+00:00</t>
+    <t>2025-02-19T13:47:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-core-vs-encounter-identifier-type.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-encounter-identifier-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-19T13:47:59+00:00</t>
+    <t>2025-02-19T13:52:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-core-vs-encounter-identifier-type.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-encounter-identifier-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-19T13:52:01+00:00</t>
+    <t>2025-02-19T13:53:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-core-vs-encounter-identifier-type.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-encounter-identifier-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-19T13:53:58+00:00</t>
+    <t>2025-02-19T13:58:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-core-vs-encounter-identifier-type.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-encounter-identifier-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-19T13:58:46+00:00</t>
+    <t>2025-02-19T14:07:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-core-vs-encounter-identifier-type.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-encounter-identifier-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-19T14:07:54+00:00</t>
+    <t>2025-02-19T14:26:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-core-vs-encounter-identifier-type.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-encounter-identifier-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-12T08:11:18+00:00</t>
+    <t>2025-05-20T13:27:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-core-vs-encounter-identifier-type.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-encounter-identifier-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-20T13:27:17+00:00</t>
+    <t>2025-05-20T13:29:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-core-vs-encounter-identifier-type.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-encounter-identifier-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-20T13:29:42+00:00</t>
+    <t>2025-05-20T13:48:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-core-vs-encounter-identifier-type.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-encounter-identifier-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-20T13:48:39+00:00</t>
+    <t>2025-06-04T13:32:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-core-vs-encounter-identifier-type.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-encounter-identifier-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-04T13:32:30+00:00</t>
+    <t>2025-06-24T17:01:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-core-vs-encounter-identifier-type.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-encounter-identifier-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-24T17:01:22+00:00</t>
+    <t>2025-07-04T12:19:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-core-vs-encounter-identifier-type.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-encounter-identifier-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-04T12:19:33+00:00</t>
+    <t>2025-07-08T13:28:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-core-vs-encounter-identifier-type.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-encounter-identifier-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-08T13:28:39+00:00</t>
+    <t>2025-07-16T09:34:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-core-vs-encounter-identifier-type.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-encounter-identifier-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-16T09:34:35+00:00</t>
+    <t>2025-07-30T14:55:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-core-vs-encounter-identifier-type.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-encounter-identifier-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-30T14:55:53+00:00</t>
+    <t>2025-10-08T07:32:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-core-vs-encounter-identifier-type.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-encounter-identifier-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-08T07:32:57+00:00</t>
+    <t>2025-10-08T12:04:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-core-vs-encounter-identifier-type.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-encounter-identifier-type.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.1.0</t>
+    <t>2.2.0-ballot</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-08T12:04:30+00:00</t>
+    <t>2025-10-08T16:01:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-core-vs-encounter-identifier-type.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-encounter-identifier-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-30T10:25:45+00:00</t>
+    <t>2026-02-04T13:09:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-core-vs-encounter-identifier-type.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-encounter-identifier-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-04T13:09:39+00:00</t>
+    <t>2026-02-09T06:47:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-core-vs-encounter-identifier-type.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-encounter-identifier-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-09T06:47:58+00:00</t>
+    <t>2026-02-11T16:15:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-core-vs-encounter-identifier-type.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-encounter-identifier-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-11T16:15:37+00:00</t>
+    <t>2026-02-17T10:02:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-core-vs-encounter-identifier-type.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-encounter-identifier-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-17T10:02:14+00:00</t>
+    <t>2026-02-23T09:26:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-core-vs-encounter-identifier-type.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-encounter-identifier-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-23T09:26:22+00:00</t>
+    <t>2026-02-23T10:39:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-core-vs-encounter-identifier-type.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-encounter-identifier-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-23T10:39:10+00:00</t>
+    <t>2026-02-23T12:56:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-core-vs-encounter-identifier-type.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-encounter-identifier-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-20T07:09:47+00:00</t>
+    <t>2026-03-25T10:22:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-core-vs-encounter-identifier-type.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-encounter-identifier-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-25T10:22:11+00:00</t>
+    <t>2026-03-25T10:22:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-core-vs-encounter-identifier-type.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-encounter-identifier-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-25T10:22:40+00:00</t>
+    <t>2026-03-25T10:25:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-core-vs-encounter-identifier-type.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-encounter-identifier-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-25T10:25:13+00:00</t>
+    <t>2026-03-25T15:00:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-core-vs-encounter-identifier-type.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-encounter-identifier-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-25T15:00:47+00:00</t>
+    <t>2026-03-31T09:16:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -81,7 +81,7 @@
     <t>Jurisdiction</t>
   </si>
   <si>
-    <t>France</t>
+    <t>France (la)</t>
   </si>
   <si>
     <t>Description</t>

--- a/main/ig/ValueSet-fr-core-vs-encounter-identifier-type.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-encounter-identifier-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-31T09:16:18+00:00</t>
+    <t>2026-05-07T06:38:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-core-vs-encounter-identifier-type.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-encounter-identifier-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-27T13:50:40+00:00</t>
+    <t>2026-05-27T14:53:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-core-vs-encounter-identifier-type.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-encounter-identifier-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-27T14:53:55+00:00</t>
+    <t>2026-05-28T14:22:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-core-vs-encounter-identifier-type.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-encounter-identifier-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-28T14:22:24+00:00</t>
+    <t>2026-06-12T14:04:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-core-vs-encounter-identifier-type.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-encounter-identifier-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-12T14:04:24+00:00</t>
+    <t>2026-06-12T14:05:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-core-vs-encounter-identifier-type.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-encounter-identifier-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-12T14:05:00+00:00</t>
+    <t>2026-06-12T14:35:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-core-vs-encounter-identifier-type.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-encounter-identifier-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-12T14:35:23+00:00</t>
+    <t>2026-06-26T12:32:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-core-vs-encounter-identifier-type.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-encounter-identifier-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-26T12:32:04+00:00</t>
+    <t>2026-06-29T09:30:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-core-vs-encounter-identifier-type.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-encounter-identifier-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T09:30:52+00:00</t>
+    <t>2026-07-22T12:21:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-core-vs-encounter-identifier-type.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-encounter-identifier-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-22T12:21:07+00:00</t>
+    <t>2026-07-27T15:02:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-core-vs-encounter-identifier-type.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-encounter-identifier-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-27T15:02:31+00:00</t>
+    <t>2026-08-03T12:52:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-core-vs-encounter-identifier-type.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-encounter-identifier-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-03T12:52:25+00:00</t>
+    <t>2026-08-04T12:22:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-core-vs-encounter-identifier-type.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-encounter-identifier-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-04T12:22:31+00:00</t>
+    <t>2026-08-04T12:29:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-core-vs-encounter-identifier-type.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-encounter-identifier-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-04T12:29:23+00:00</t>
+    <t>2026-08-10T16:34:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
